--- a/data/expevo_2026_samplemetadata.xlsx
+++ b/data/expevo_2026_samplemetadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanbergland/Documents/GitHub/CompEvoBio_modules/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C927BE-2EA0-FA4A-8D32-60622A61BF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91442570-7B89-0842-8CF6-0F1233A649BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17260" xr2:uid="{58CE3B1C-FF9A-9A42-B209-E999AB6E56E5}"/>
+    <workbookView xWindow="4080" yWindow="620" windowWidth="30240" windowHeight="17260" xr2:uid="{58CE3B1C-FF9A-9A42-B209-E999AB6E56E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="374">
   <si>
     <t>sampleId</t>
   </si>
@@ -1060,6 +1060,105 @@
   </si>
   <si>
     <t>ERR442901</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_CP_1_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>ExpEco</t>
+  </si>
+  <si>
+    <t>IlluminaHiSeq2000</t>
+  </si>
+  <si>
+    <t>SRR1988514</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093%2Fmolbev%2Fmsv136</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_CP2_2_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SRR1988516</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_CP3_3_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SRR1988515</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_LEP_1_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>LEP</t>
+  </si>
+  <si>
+    <t>large</t>
+  </si>
+  <si>
+    <t>SRR1988510</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_LEP_2_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SRR1988512</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_LEP_3_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SRR1988513</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_SBP_1_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SBP</t>
+  </si>
+  <si>
+    <t>starting</t>
+  </si>
+  <si>
+    <t>SRR1988509</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_SEP_1_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SEP</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>SRR1988517</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_SEP_2_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>SRR1988518</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_SEP_3_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>IlluminaHiSeq2001</t>
+  </si>
+  <si>
+    <t>SRR1988519</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1212,6 +1311,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1526,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6F86A2-1638-7A42-AFAB-3C5B4448F588}">
-  <dimension ref="A1:Z93"/>
+  <dimension ref="A1:Z103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
@@ -8426,6 +8526,746 @@
       </c>
       <c r="X93" s="2" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26">
+      <c r="A94" t="s">
+        <v>341</v>
+      </c>
+      <c r="B94" t="s">
+        <v>342</v>
+      </c>
+      <c r="C94">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D94">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E94" t="s">
+        <v>26</v>
+      </c>
+      <c r="F94" t="s">
+        <v>27</v>
+      </c>
+      <c r="G94" t="s">
+        <v>343</v>
+      </c>
+      <c r="H94" t="s">
+        <v>344</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>365</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>12</v>
+      </c>
+      <c r="M94">
+        <v>2015</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>31</v>
+      </c>
+      <c r="R94" t="s">
+        <v>31</v>
+      </c>
+      <c r="S94">
+        <v>1000</v>
+      </c>
+      <c r="T94" t="s">
+        <v>32</v>
+      </c>
+      <c r="U94" t="s">
+        <v>345</v>
+      </c>
+      <c r="V94" t="s">
+        <v>346</v>
+      </c>
+      <c r="W94" t="s">
+        <v>347</v>
+      </c>
+      <c r="X94" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26">
+      <c r="A95" t="s">
+        <v>349</v>
+      </c>
+      <c r="B95" t="s">
+        <v>342</v>
+      </c>
+      <c r="C95">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D95">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E95" t="s">
+        <v>26</v>
+      </c>
+      <c r="F95" t="s">
+        <v>27</v>
+      </c>
+      <c r="G95" t="s">
+        <v>343</v>
+      </c>
+      <c r="H95" t="s">
+        <v>344</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>365</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>12</v>
+      </c>
+      <c r="M95">
+        <v>2015</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95">
+        <v>2</v>
+      </c>
+      <c r="P95" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>31</v>
+      </c>
+      <c r="R95" t="s">
+        <v>31</v>
+      </c>
+      <c r="S95">
+        <v>1000</v>
+      </c>
+      <c r="T95" t="s">
+        <v>32</v>
+      </c>
+      <c r="U95" t="s">
+        <v>345</v>
+      </c>
+      <c r="V95" t="s">
+        <v>346</v>
+      </c>
+      <c r="W95" t="s">
+        <v>350</v>
+      </c>
+      <c r="X95" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26">
+      <c r="A96" t="s">
+        <v>351</v>
+      </c>
+      <c r="B96" t="s">
+        <v>342</v>
+      </c>
+      <c r="C96">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D96">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E96" t="s">
+        <v>26</v>
+      </c>
+      <c r="F96" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" t="s">
+        <v>343</v>
+      </c>
+      <c r="H96" t="s">
+        <v>344</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>365</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>12</v>
+      </c>
+      <c r="M96">
+        <v>2015</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="O96">
+        <v>3</v>
+      </c>
+      <c r="P96" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>31</v>
+      </c>
+      <c r="R96" t="s">
+        <v>31</v>
+      </c>
+      <c r="S96">
+        <v>1000</v>
+      </c>
+      <c r="T96" t="s">
+        <v>32</v>
+      </c>
+      <c r="U96" t="s">
+        <v>345</v>
+      </c>
+      <c r="V96" t="s">
+        <v>346</v>
+      </c>
+      <c r="W96" t="s">
+        <v>352</v>
+      </c>
+      <c r="X96" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24">
+      <c r="A97" t="s">
+        <v>353</v>
+      </c>
+      <c r="B97" t="s">
+        <v>354</v>
+      </c>
+      <c r="C97">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D97">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E97" t="s">
+        <v>26</v>
+      </c>
+      <c r="F97" t="s">
+        <v>27</v>
+      </c>
+      <c r="G97" t="s">
+        <v>343</v>
+      </c>
+      <c r="H97" t="s">
+        <v>344</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>365</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>12</v>
+      </c>
+      <c r="M97">
+        <v>2015</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97">
+        <v>1</v>
+      </c>
+      <c r="P97" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>31</v>
+      </c>
+      <c r="R97" t="s">
+        <v>31</v>
+      </c>
+      <c r="S97">
+        <v>1000</v>
+      </c>
+      <c r="T97" t="s">
+        <v>32</v>
+      </c>
+      <c r="U97" t="s">
+        <v>345</v>
+      </c>
+      <c r="V97" t="s">
+        <v>346</v>
+      </c>
+      <c r="W97" t="s">
+        <v>356</v>
+      </c>
+      <c r="X97" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24">
+      <c r="A98" t="s">
+        <v>357</v>
+      </c>
+      <c r="B98" t="s">
+        <v>354</v>
+      </c>
+      <c r="C98">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D98">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E98" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" t="s">
+        <v>27</v>
+      </c>
+      <c r="G98" t="s">
+        <v>343</v>
+      </c>
+      <c r="H98" t="s">
+        <v>344</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>365</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>12</v>
+      </c>
+      <c r="M98">
+        <v>2015</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>2</v>
+      </c>
+      <c r="P98" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>31</v>
+      </c>
+      <c r="R98" t="s">
+        <v>31</v>
+      </c>
+      <c r="S98">
+        <v>1000</v>
+      </c>
+      <c r="T98" t="s">
+        <v>32</v>
+      </c>
+      <c r="U98" t="s">
+        <v>345</v>
+      </c>
+      <c r="V98" t="s">
+        <v>346</v>
+      </c>
+      <c r="W98" t="s">
+        <v>358</v>
+      </c>
+      <c r="X98" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24">
+      <c r="A99" t="s">
+        <v>359</v>
+      </c>
+      <c r="B99" t="s">
+        <v>354</v>
+      </c>
+      <c r="C99">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D99">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E99" t="s">
+        <v>26</v>
+      </c>
+      <c r="F99" t="s">
+        <v>27</v>
+      </c>
+      <c r="G99" t="s">
+        <v>343</v>
+      </c>
+      <c r="H99" t="s">
+        <v>344</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>365</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>12</v>
+      </c>
+      <c r="M99">
+        <v>2015</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99">
+        <v>3</v>
+      </c>
+      <c r="P99" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>31</v>
+      </c>
+      <c r="R99" t="s">
+        <v>31</v>
+      </c>
+      <c r="S99">
+        <v>1000</v>
+      </c>
+      <c r="T99" t="s">
+        <v>32</v>
+      </c>
+      <c r="U99" t="s">
+        <v>345</v>
+      </c>
+      <c r="V99" t="s">
+        <v>346</v>
+      </c>
+      <c r="W99" t="s">
+        <v>360</v>
+      </c>
+      <c r="X99" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24">
+      <c r="A100" t="s">
+        <v>361</v>
+      </c>
+      <c r="B100" t="s">
+        <v>362</v>
+      </c>
+      <c r="C100">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D100">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E100" t="s">
+        <v>26</v>
+      </c>
+      <c r="F100" t="s">
+        <v>27</v>
+      </c>
+      <c r="G100" t="s">
+        <v>343</v>
+      </c>
+      <c r="H100" t="s">
+        <v>344</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>365</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>12</v>
+      </c>
+      <c r="M100">
+        <v>2015</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>31</v>
+      </c>
+      <c r="R100" t="s">
+        <v>31</v>
+      </c>
+      <c r="S100">
+        <v>1000</v>
+      </c>
+      <c r="T100" t="s">
+        <v>32</v>
+      </c>
+      <c r="U100" t="s">
+        <v>345</v>
+      </c>
+      <c r="V100" t="s">
+        <v>346</v>
+      </c>
+      <c r="W100" t="s">
+        <v>364</v>
+      </c>
+      <c r="X100" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24">
+      <c r="A101" t="s">
+        <v>365</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C101">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D101">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E101" t="s">
+        <v>26</v>
+      </c>
+      <c r="F101" t="s">
+        <v>27</v>
+      </c>
+      <c r="G101" t="s">
+        <v>343</v>
+      </c>
+      <c r="H101" t="s">
+        <v>344</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>365</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>12</v>
+      </c>
+      <c r="M101">
+        <v>2015</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="P101" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>31</v>
+      </c>
+      <c r="R101" t="s">
+        <v>31</v>
+      </c>
+      <c r="S101">
+        <v>1000</v>
+      </c>
+      <c r="T101" t="s">
+        <v>32</v>
+      </c>
+      <c r="U101" t="s">
+        <v>345</v>
+      </c>
+      <c r="V101" t="s">
+        <v>346</v>
+      </c>
+      <c r="W101" t="s">
+        <v>368</v>
+      </c>
+      <c r="X101" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24">
+      <c r="A102" t="s">
+        <v>369</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C102">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D102">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E102" t="s">
+        <v>26</v>
+      </c>
+      <c r="F102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G102" t="s">
+        <v>343</v>
+      </c>
+      <c r="H102" t="s">
+        <v>344</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>365</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>12</v>
+      </c>
+      <c r="M102">
+        <v>2015</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102">
+        <v>2</v>
+      </c>
+      <c r="P102" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>31</v>
+      </c>
+      <c r="R102" t="s">
+        <v>31</v>
+      </c>
+      <c r="S102">
+        <v>1000</v>
+      </c>
+      <c r="T102" t="s">
+        <v>32</v>
+      </c>
+      <c r="U102" t="s">
+        <v>345</v>
+      </c>
+      <c r="V102" t="s">
+        <v>346</v>
+      </c>
+      <c r="W102" t="s">
+        <v>370</v>
+      </c>
+      <c r="X102" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24">
+      <c r="A103" t="s">
+        <v>371</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C103">
+        <v>41.878100000000003</v>
+      </c>
+      <c r="D103">
+        <v>-87.629800000000003</v>
+      </c>
+      <c r="E103" t="s">
+        <v>26</v>
+      </c>
+      <c r="F103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G103" t="s">
+        <v>343</v>
+      </c>
+      <c r="H103" t="s">
+        <v>344</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>365</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>12</v>
+      </c>
+      <c r="M103">
+        <v>2015</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <v>3</v>
+      </c>
+      <c r="P103" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>31</v>
+      </c>
+      <c r="R103" t="s">
+        <v>31</v>
+      </c>
+      <c r="S103">
+        <v>1000</v>
+      </c>
+      <c r="T103" t="s">
+        <v>32</v>
+      </c>
+      <c r="U103" t="s">
+        <v>345</v>
+      </c>
+      <c r="V103" t="s">
+        <v>372</v>
+      </c>
+      <c r="W103" t="s">
+        <v>373</v>
+      </c>
+      <c r="X103" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/data/expevo_2026_samplemetadata.xlsx
+++ b/data/expevo_2026_samplemetadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanbergland/Documents/GitHub/CompEvoBio_modules/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91442570-7B89-0842-8CF6-0F1233A649BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6C9A96-E5EF-914A-AF9E-F801FEFFE547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="620" windowWidth="30240" windowHeight="17260" xr2:uid="{58CE3B1C-FF9A-9A42-B209-E999AB6E56E5}"/>
   </bookViews>
@@ -1086,15 +1086,9 @@
     <t>https://doi.org/10.1093%2Fmolbev%2Fmsv136</t>
   </si>
   <si>
-    <t>ExpEco_PRJNA281953_CP2_2_2015-MM-DD</t>
-  </si>
-  <si>
     <t>SRR1988516</t>
   </si>
   <si>
-    <t>ExpEco_PRJNA281953_CP3_3_2015-MM-DD</t>
-  </si>
-  <si>
     <t>SRR1988515</t>
   </si>
   <si>
@@ -1159,6 +1153,12 @@
   </si>
   <si>
     <t>SRR1988519</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_CP_2_2015-MM-DD</t>
+  </si>
+  <si>
+    <t>ExpEco_PRJNA281953_CP_3_2015-MM-DD</t>
   </si>
 </sst>
 </file>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="95" spans="1:26">
       <c r="A95" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="B95" t="s">
         <v>342</v>
@@ -8670,7 +8670,7 @@
         <v>346</v>
       </c>
       <c r="W95" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X95" t="s">
         <v>348</v>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="96" spans="1:26">
       <c r="A96" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B96" t="s">
         <v>342</v>
@@ -8744,7 +8744,7 @@
         <v>346</v>
       </c>
       <c r="W96" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="X96" t="s">
         <v>348</v>
@@ -8752,10 +8752,10 @@
     </row>
     <row r="97" spans="1:24">
       <c r="A97" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B97" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C97">
         <v>41.878100000000003</v>
@@ -8797,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q97" t="s">
         <v>31</v>
@@ -8818,7 +8818,7 @@
         <v>346</v>
       </c>
       <c r="W97" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="X97" t="s">
         <v>348</v>
@@ -8826,10 +8826,10 @@
     </row>
     <row r="98" spans="1:24">
       <c r="A98" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B98" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C98">
         <v>41.878100000000003</v>
@@ -8871,7 +8871,7 @@
         <v>2</v>
       </c>
       <c r="P98" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q98" t="s">
         <v>31</v>
@@ -8892,7 +8892,7 @@
         <v>346</v>
       </c>
       <c r="W98" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="X98" t="s">
         <v>348</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="99" spans="1:24">
       <c r="A99" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B99" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C99">
         <v>41.878100000000003</v>
@@ -8945,7 +8945,7 @@
         <v>3</v>
       </c>
       <c r="P99" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q99" t="s">
         <v>31</v>
@@ -8966,7 +8966,7 @@
         <v>346</v>
       </c>
       <c r="W99" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="X99" t="s">
         <v>348</v>
@@ -8974,10 +8974,10 @@
     </row>
     <row r="100" spans="1:24">
       <c r="A100" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B100" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C100">
         <v>41.878100000000003</v>
@@ -9019,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q100" t="s">
         <v>31</v>
@@ -9040,7 +9040,7 @@
         <v>346</v>
       </c>
       <c r="W100" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="X100" t="s">
         <v>348</v>
@@ -9048,10 +9048,10 @@
     </row>
     <row r="101" spans="1:24">
       <c r="A101" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C101">
         <v>41.878100000000003</v>
@@ -9093,7 +9093,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q101" t="s">
         <v>31</v>
@@ -9114,7 +9114,7 @@
         <v>346</v>
       </c>
       <c r="W101" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X101" t="s">
         <v>348</v>
@@ -9122,10 +9122,10 @@
     </row>
     <row r="102" spans="1:24">
       <c r="A102" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C102">
         <v>41.878100000000003</v>
@@ -9167,7 +9167,7 @@
         <v>2</v>
       </c>
       <c r="P102" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q102" t="s">
         <v>31</v>
@@ -9188,7 +9188,7 @@
         <v>346</v>
       </c>
       <c r="W102" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="X102" t="s">
         <v>348</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="103" spans="1:24">
       <c r="A103" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C103">
         <v>41.878100000000003</v>
@@ -9241,7 +9241,7 @@
         <v>3</v>
       </c>
       <c r="P103" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q103" t="s">
         <v>31</v>
@@ -9259,10 +9259,10 @@
         <v>345</v>
       </c>
       <c r="V103" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W103" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="X103" t="s">
         <v>348</v>
